--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 97 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 96 clubs short</t>
         </is>
       </c>
     </row>
@@ -3108,8 +3108,8 @@
       <c r="W24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X24" s="9" t="n">
-        <v>2</v>
+      <c r="X24" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y24" s="9" t="n">
         <v>0</v>
@@ -3420,7 +3420,7 @@
         <v>0</v>
       </c>
       <c r="X27" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y27" s="9" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         </is>
       </c>
       <c r="P29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" s="9" t="n">
         <v>0</v>
@@ -6679,7 +6679,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T59" s="9" t="n">
         <v>0</v>
@@ -9283,7 +9283,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9353,8 +9353,8 @@
       <c r="Y85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z85" s="9" t="n">
-        <v>0</v>
+      <c r="Z85" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA85" s="10" t="n">
         <v>1</v>
@@ -9654,7 +9654,7 @@
         <v>1</v>
       </c>
       <c r="U88" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V88" s="9" t="n">
         <v>0</v>
@@ -13222,7 +13222,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -16822,7 +16822,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -19003,7 +19003,7 @@
         <v>2</v>
       </c>
       <c r="Q181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" s="9" t="n">
         <v>0</v>
@@ -20014,7 +20014,7 @@
         </is>
       </c>
       <c r="P191" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q191" s="9" t="n">
         <v>0</v>
@@ -21801,7 +21801,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,11 @@
       <c r="AB39" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC39" s="4" t="inlineStr"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5177,7 +5181,11 @@
       <c r="AB44" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -5383,7 +5391,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -5484,7 +5496,11 @@
       <c r="AB47" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -5892,7 +5908,11 @@
       <c r="AB51" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC51" s="4" t="inlineStr"/>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -6708,7 +6728,11 @@
       <c r="AB59" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC59" s="4" t="inlineStr"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -6910,7 +6934,11 @@
       <c r="AB61" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC61" s="4" t="inlineStr"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7728,7 +7756,11 @@
       <c r="AB69" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -8542,7 +8574,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -9677,7 +9713,11 @@
       <c r="AB88" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -11111,7 +11151,11 @@
       <c r="AB102" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC102" s="4" t="inlineStr"/>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -11826,7 +11870,11 @@
       <c r="AB109" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -12242,7 +12290,11 @@
       <c r="AB113" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC113" s="4" t="inlineStr"/>
+      <c r="AC113" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -12545,7 +12597,11 @@
       <c r="AB116" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -13159,7 +13215,11 @@
       <c r="AB122" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC122" s="4" t="inlineStr"/>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -14383,7 +14443,11 @@
       <c r="AB134" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -19038,7 +19102,11 @@
       <c r="AB181" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC181" s="4" t="inlineStr"/>
+      <c r="AC181" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -19543,7 +19611,11 @@
       <c r="AB186" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC186" s="4" t="inlineStr"/>
+      <c r="AC186" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -19951,7 +20023,11 @@
       <c r="AB190" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC190" s="4" t="inlineStr"/>
+      <c r="AC190" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -20670,7 +20746,11 @@
       <c r="AB197" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC197" s="4" t="inlineStr"/>
+      <c r="AC197" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -20771,7 +20851,11 @@
       <c r="AB198" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC198" s="4" t="inlineStr"/>
+      <c r="AC198" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="inlineStr">

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 96 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 86 clubs short</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1413,8 +1413,8 @@
       <c r="Y7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z7" s="9" t="n">
-        <v>0</v>
+      <c r="Z7" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA7" s="10" t="n">
         <v>1</v>
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>10</v>
@@ -1710,8 +1710,8 @@
       <c r="Y10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" s="9" t="n">
-        <v>0</v>
+      <c r="Z10" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA10" s="10" t="n">
         <v>1</v>
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="P46" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q46" s="9" t="n">
         <v>0</v>
@@ -5368,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="U46" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V46" s="9" t="n">
         <v>0</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -7135,8 +7135,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="10" t="n">
         <v>1</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -9012,7 +9012,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -9082,8 +9082,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -9739,7 +9739,7 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" s="6" t="n">
         <v>10</v>
@@ -9809,8 +9809,8 @@
       <c r="Y89" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z89" s="9" t="n">
-        <v>0</v>
+      <c r="Z89" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA89" s="10" t="n">
         <v>1</v>
@@ -13851,7 +13851,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13921,8 +13921,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14539,8 +14539,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -14667,7 +14667,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14737,8 +14737,8 @@
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="9" t="n">
-        <v>0</v>
+      <c r="Z137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14978,13 +14978,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -16009,8 +16009,8 @@
       <c r="T150" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U150" s="9" t="n">
-        <v>0</v>
+      <c r="U150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V150" s="9" t="n">
         <v>0</v>
@@ -16024,8 +16024,8 @@
       <c r="Y150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z150" s="9" t="n">
-        <v>0</v>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA150" s="10" t="n">
         <v>1</v>
@@ -16251,7 +16251,7 @@
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16321,8 +16321,8 @@
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="9" t="n">
-        <v>0</v>
+      <c r="Z153" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
@@ -21390,7 +21390,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21753,7 +21753,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -21852,7 +21852,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -22182,7 +22182,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -22248,7 +22248,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22314,7 +22314,7 @@
         <v>5</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$202</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$203</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 86 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 55 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC202"/>
+  <dimension ref="A1:AC203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -918,8 +918,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="S3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" s="9" t="n">
         <v>0</v>
@@ -1017,8 +1017,8 @@
       <c r="Y3" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" s="9" t="n">
-        <v>0</v>
+      <c r="Z3" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA3" s="10" t="n">
         <v>1</v>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1215,8 +1215,8 @@
       <c r="Y5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z5" s="9" t="n">
-        <v>0</v>
+      <c r="Z5" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA5" s="10" t="n">
         <v>1</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1512,8 +1512,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>1</v>
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1809,8 +1809,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1908,8 +1908,8 @@
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2036,7 +2036,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2085,8 +2085,8 @@
       <c r="R14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="9" t="n">
-        <v>1</v>
+      <c r="S14" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T14" s="10" t="n">
         <v>1</v>
@@ -2106,8 +2106,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="10" t="n">
         <v>1</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2304,8 +2304,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -2432,7 +2432,7 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>10</v>
@@ -2502,8 +2502,8 @@
       <c r="Y18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z18" s="9" t="n">
-        <v>0</v>
+      <c r="Z18" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA18" s="10" t="n">
         <v>1</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2908,8 +2908,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -5149,7 +5149,7 @@
         <v>2</v>
       </c>
       <c r="R44" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" s="9" t="n">
         <v>0</v>
@@ -5353,16 +5353,16 @@
         </is>
       </c>
       <c r="P46" s="10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T46" s="10" t="n">
         <v>1</v>
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5697,8 +5697,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="9" t="n">
-        <v>0</v>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6105,8 +6105,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="9" t="n">
-        <v>0</v>
+      <c r="Z53" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6206,8 +6206,8 @@
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
@@ -6392,7 +6392,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T56" s="9" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6517,8 +6517,8 @@
       <c r="Y57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z57" s="9" t="n">
-        <v>0</v>
+      <c r="Z57" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA57" s="10" t="n">
         <v>1</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6719,8 +6719,8 @@
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="9" t="n">
-        <v>0</v>
+      <c r="Z59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -7877,7 +7877,7 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>The Lectern KL</t>
+          <t>The Lectern KL Toastmasters Club</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8565,8 +8565,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8847,7 +8847,7 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
         <v>0</v>
@@ -8957,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="S81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81" s="9" t="n">
         <v>0</v>
@@ -9529,7 +9529,7 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9569,8 +9569,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P87" s="9" t="n">
-        <v>3</v>
+      <c r="P87" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q87" s="9" t="n">
         <v>1</v>
@@ -9599,8 +9599,8 @@
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA87" s="10" t="n">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88" s="6" t="n">
         <v>10</v>
@@ -9683,14 +9683,14 @@
       <c r="R88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S88" s="9" t="n">
-        <v>1</v>
+      <c r="S88" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T88" s="10" t="n">
         <v>1</v>
       </c>
       <c r="U88" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V88" s="9" t="n">
         <v>0</v>
@@ -9949,7 +9949,7 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -10019,8 +10019,8 @@
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -10068,13 +10068,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>4</v>
       </c>
       <c r="W92" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X92" s="10" t="n">
         <v>5</v>
@@ -10361,7 +10361,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -10431,8 +10431,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -10462,7 +10462,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10532,8 +10532,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10728,8 +10728,8 @@
       <c r="W98" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X98" s="9" t="n">
-        <v>3</v>
+      <c r="X98" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10971,7 +10971,7 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F101" s="6" t="n">
         <v>10</v>
@@ -11023,8 +11023,8 @@
       <c r="S101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T101" s="9" t="n">
-        <v>0</v>
+      <c r="T101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U101" s="9" t="n">
         <v>0</v>
@@ -11041,8 +11041,8 @@
       <c r="Y101" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z101" s="9" t="n">
-        <v>0</v>
+      <c r="Z101" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA101" s="10" t="n">
         <v>1</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -11424,7 +11424,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -11910,13 +11910,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -12261,7 +12261,7 @@
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="10" t="n">
         <v>1</v>
@@ -12417,7 +12417,7 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -12487,8 +12487,8 @@
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="9" t="n">
-        <v>0</v>
+      <c r="Z115" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA115" s="10" t="n">
         <v>1</v>
@@ -13136,7 +13136,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13191,8 +13191,8 @@
       <c r="T122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U122" s="9" t="n">
-        <v>0</v>
+      <c r="U122" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V122" s="9" t="n">
         <v>3</v>
@@ -13311,8 +13311,8 @@
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="9" t="n">
-        <v>0</v>
+      <c r="Z123" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA123" s="9" t="n">
         <v>0</v>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13517,8 +13517,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -14045,15 +14045,15 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>4388</v>
+        <v>28680653</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Butterworth Club</t>
+          <t>AT &amp; S Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14067,13 +14067,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         </is>
       </c>
       <c r="P131" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q131" s="9" t="n">
         <v>0</v>
@@ -14111,32 +14111,26 @@
       <c r="U131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V131" s="10" t="n">
-        <v>4</v>
+      <c r="V131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="10" t="n">
-        <v>6</v>
+      <c r="X131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="10" t="n">
-        <v>1</v>
+      <c r="Z131" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB131" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC131" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+      <c r="AB131" s="4" t="n"/>
+      <c r="AC131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -14150,15 +14144,15 @@
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>3746255</v>
+        <v>4388</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>FYS Toastmasters Club</t>
+          <t>Butterworth Club</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14172,17 +14166,17 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L132" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M132" s="8" t="n">
@@ -14210,20 +14204,20 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U132" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V132" s="9" t="n">
-        <v>2</v>
+      <c r="T132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X132" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
@@ -14235,11 +14229,11 @@
         <v>1</v>
       </c>
       <c r="AB132" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC132" s="4" t="inlineStr">
         <is>
-          <t>Select Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -14255,35 +14249,35 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>28678991</v>
+        <v>3746255</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>KTPC Toastmasters Club</t>
+          <t>FYS Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="J133" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K133" s="4" t="n">
         <v>2</v>
-      </c>
-      <c r="F133" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G133" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="J133" s="4" t="n">
-        <v>12</v>
-      </c>
-      <c r="K133" s="4" t="n">
-        <v>0</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14303,8 +14297,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P133" s="10" t="n">
-        <v>4</v>
+      <c r="P133" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Q133" s="9" t="n">
         <v>0</v>
@@ -14315,20 +14309,20 @@
       <c r="S133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" s="9" t="n">
-        <v>0</v>
+      <c r="T133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U133" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X133" s="9" t="n">
-        <v>0</v>
+      <c r="X133" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y133" s="9" t="n">
         <v>0</v>
@@ -14340,9 +14334,13 @@
         <v>1</v>
       </c>
       <c r="AB133" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC133" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC133" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -14356,15 +14354,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>9372</v>
+        <v>28678991</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Seberang Jaya Toastmasters Club</t>
+          <t>KTPC Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -14378,17 +14376,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -14404,11 +14402,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P134" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q134" s="9" t="n">
-        <v>0</v>
+      <c r="P134" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q134" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -14422,14 +14420,14 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="10" t="n">
-        <v>4</v>
+      <c r="V134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="X134" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X134" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -14441,35 +14439,31 @@
         <v>1</v>
       </c>
       <c r="AB134" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC134" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>925535</v>
+        <v>9372</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai Toastmasters Club</t>
+          <t>Seberang Jaya Toastmasters Club</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14483,17 +14477,17 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M135" s="8" t="n">
@@ -14510,7 +14504,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -14519,7 +14513,7 @@
         <v>0</v>
       </c>
       <c r="S135" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T135" s="9" t="n">
         <v>0</v>
@@ -14527,14 +14521,14 @@
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V135" s="9" t="n">
-        <v>0</v>
+      <c r="V135" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W135" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -14545,8 +14539,14 @@
       <c r="AA135" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB135" s="4" t="n"/>
-      <c r="AC135" s="4" t="inlineStr"/>
+      <c r="AB135" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC135" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -14560,15 +14560,15 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>7436254</v>
+        <v>925535</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Chiang Rai Toastmasters Club</t>
+          <t>Chiang Mai Toastmasters Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14618,7 +14618,7 @@
         <v>0</v>
       </c>
       <c r="S136" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T136" s="9" t="n">
         <v>0</v>
@@ -14633,13 +14633,13 @@
         <v>0</v>
       </c>
       <c r="X136" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -14659,15 +14659,15 @@
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>28676370</v>
+        <v>7436254</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>CMU Alumni Toastmasters</t>
+          <t>Chiang Rai Toastmasters Club</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -14681,10 +14681,10 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
         <v>0</v>
@@ -14732,13 +14732,13 @@
         <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
+      <c r="Z137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14758,15 +14758,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>28679270</v>
+        <v>28676370</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Gryffindor Toastmasters Club</t>
+          <t>CMU Alumni Toastmasters</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14780,10 +14780,10 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K138" s="4" t="n">
         <v>0</v>
@@ -14794,11 +14794,11 @@
         </is>
       </c>
       <c r="M138" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N138" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O138" s="7" t="inlineStr">
@@ -14830,17 +14830,17 @@
       <c r="W138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X138" s="9" t="n">
-        <v>0</v>
+      <c r="X138" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z138" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA138" s="9" t="n">
-        <v>0</v>
+      <c r="Z138" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB138" s="4" t="n"/>
       <c r="AC138" s="4" t="inlineStr"/>
@@ -14857,11 +14857,11 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>7698434</v>
+        <v>28679270</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Lamphun Toastmasters Club</t>
+          <t>Gryffindor Toastmasters Club</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
@@ -14879,10 +14879,10 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K139" s="4" t="n">
         <v>0</v>
@@ -14893,11 +14893,11 @@
         </is>
       </c>
       <c r="M139" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O139" s="7" t="inlineStr">
@@ -14929,8 +14929,8 @@
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="10" t="n">
-        <v>4</v>
+      <c r="X139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
@@ -14938,8 +14938,8 @@
       <c r="Z139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA139" s="10" t="n">
-        <v>1</v>
+      <c r="AA139" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB139" s="4" t="n"/>
       <c r="AC139" s="4" t="inlineStr"/>
@@ -14956,15 +14956,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>7805051</v>
+        <v>7698434</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>NU Toastmasters</t>
+          <t>Lamphun Toastmasters Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14978,13 +14978,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15023,19 +15023,19 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X140" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="9" t="n">
-        <v>0</v>
+      <c r="Z140" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA140" s="10" t="n">
         <v>1</v>
@@ -15055,15 +15055,15 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>28677151</v>
+        <v>7805051</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Thailand Laughter Toastmaster</t>
+          <t>NU Toastmasters</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -15077,13 +15077,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15122,19 +15122,19 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z141" s="10" t="n">
-        <v>1</v>
+      <c r="Z141" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA141" s="10" t="n">
         <v>1</v>
@@ -15150,15 +15150,15 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>2010</v>
+        <v>28677151</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Bangkok Toastmasters Club</t>
+          <t>Thailand Laughter Toastmaster</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -15176,17 +15176,17 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L142" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M142" s="8" t="n">
@@ -15203,10 +15203,10 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
@@ -15221,7 +15221,7 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
@@ -15253,15 +15253,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>28679271</v>
+        <v>2010</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Hufflepuff Toastmasters Club</t>
+          <t>Bangkok Toastmasters Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15275,25 +15275,25 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N143" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O143" s="7" t="inlineStr">
@@ -15302,10 +15302,10 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -15320,22 +15320,22 @@
         <v>0</v>
       </c>
       <c r="V143" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X143" s="9" t="n">
-        <v>0</v>
+      <c r="X143" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA143" s="9" t="n">
-        <v>0</v>
+      <c r="Z143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB143" s="4" t="n"/>
       <c r="AC143" s="4" t="inlineStr"/>
@@ -15352,11 +15352,11 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>28677547</v>
+        <v>28679271</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Pattaya Toastmasters Club</t>
+          <t>Hufflepuff Toastmasters Club</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
@@ -15374,13 +15374,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L144" s="7" t="inlineStr">
         <is>
@@ -15419,13 +15419,13 @@
         <v>0</v>
       </c>
       <c r="V144" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W144" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X144" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -15451,15 +15451,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>4386732</v>
+        <v>28677547</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Rajavithi Hospital Toastmasters Club</t>
+          <t>Pattaya Toastmasters Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15473,17 +15473,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="L145" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L145" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -15517,14 +15517,14 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W145" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X145" s="10" t="n">
-        <v>4</v>
+      <c r="V145" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W145" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
@@ -15550,15 +15550,15 @@
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>2474648</v>
+        <v>4386732</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>SpeakZy Toastmasters</t>
+          <t>Rajavithi Hospital Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -15572,25 +15572,25 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L146" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>8</v>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M146" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N146" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O146" s="7" t="inlineStr">
@@ -15616,23 +15616,23 @@
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W146" s="9" t="n">
-        <v>0</v>
+      <c r="V146" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W146" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X146" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA146" s="10" t="n">
-        <v>1</v>
+      <c r="Z146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB146" s="4" t="n"/>
       <c r="AC146" s="4" t="inlineStr"/>
@@ -15649,15 +15649,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>7328529</v>
+        <v>2474648</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Thailand Online Toastmasters Club</t>
+          <t>SpeakZy Toastmasters</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -15671,10 +15671,10 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K147" s="4" t="n">
         <v>0</v>
@@ -15698,22 +15698,22 @@
         </is>
       </c>
       <c r="P147" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q147" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S147" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T147" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U147" s="10" t="n">
-        <v>1</v>
+      <c r="S147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
         <v>0</v>
@@ -15722,13 +15722,13 @@
         <v>0</v>
       </c>
       <c r="X147" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="10" t="n">
-        <v>1</v>
+      <c r="Z147" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA147" s="10" t="n">
         <v>1</v>
@@ -15748,15 +15748,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>943943</v>
+        <v>7328529</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>The First Thai Toastmasters Club</t>
+          <t>Thailand Online Toastmasters Club</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15770,13 +15770,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15797,31 +15797,31 @@
         </is>
       </c>
       <c r="P148" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q148" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T148" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U148" s="9" t="n">
-        <v>0</v>
+      <c r="S148" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="9" t="n">
-        <v>3</v>
+      <c r="X148" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15843,19 +15843,19 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>2092</v>
+        <v>943943</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Capitol Toastmasters Club</t>
+          <t>The First Thai Toastmasters Club</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15869,17 +15869,17 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L149" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L149" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M149" s="8" t="n">
@@ -15896,10 +15896,10 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q149" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R149" s="9" t="n">
         <v>0</v>
@@ -15907,20 +15907,20 @@
       <c r="S149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T149" s="10" t="n">
-        <v>1</v>
+      <c r="T149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="10" t="n">
-        <v>4</v>
+      <c r="V149" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="W149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X149" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="X149" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -15946,11 +15946,11 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>5025753</v>
+        <v>2092</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Holy Redeemer Toastmasters Club</t>
+          <t>Capitol Toastmasters Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
@@ -15968,17 +15968,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L150" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -15998,28 +15998,28 @@
         <v>1</v>
       </c>
       <c r="Q150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S150" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T150" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U150" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V150" s="9" t="n">
-        <v>0</v>
+      <c r="U150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X150" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y150" s="9" t="n">
         <v>0</v>
@@ -16045,15 +16045,15 @@
         </is>
       </c>
       <c r="C151" s="4" t="n">
-        <v>28679272</v>
+        <v>5025753</v>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Ravenclaw Toastmasters Club</t>
+          <t>Holy Redeemer Toastmasters Club</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F151" s="6" t="n">
         <v>10</v>
@@ -16067,10 +16067,10 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J151" s="4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K151" s="4" t="n">
         <v>0</v>
@@ -16081,11 +16081,11 @@
         </is>
       </c>
       <c r="M151" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N151" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O151" s="7" t="inlineStr">
@@ -16094,7 +16094,7 @@
         </is>
       </c>
       <c r="P151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q151" s="9" t="n">
         <v>0</v>
@@ -16103,13 +16103,13 @@
         <v>0</v>
       </c>
       <c r="S151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V151" s="9" t="n">
         <v>0</v>
@@ -16117,17 +16117,17 @@
       <c r="W151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X151" s="9" t="n">
-        <v>0</v>
+      <c r="X151" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y151" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z151" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA151" s="9" t="n">
-        <v>0</v>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA151" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB151" s="4" t="n"/>
       <c r="AC151" s="4" t="inlineStr"/>
@@ -16144,11 +16144,11 @@
         </is>
       </c>
       <c r="C152" s="4" t="n">
-        <v>5040</v>
+        <v>28679272</v>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Siam Toastmasters Club</t>
+          <t>Ravenclaw Toastmasters Club</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
@@ -16166,10 +16166,10 @@
         </is>
       </c>
       <c r="I152" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J152" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K152" s="4" t="n">
         <v>0</v>
@@ -16180,11 +16180,11 @@
         </is>
       </c>
       <c r="M152" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N152" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O152" s="7" t="inlineStr">
@@ -16196,7 +16196,7 @@
         <v>0</v>
       </c>
       <c r="Q152" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R152" s="9" t="n">
         <v>0</v>
@@ -16217,7 +16217,7 @@
         <v>0</v>
       </c>
       <c r="X152" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y152" s="9" t="n">
         <v>0</v>
@@ -16225,8 +16225,8 @@
       <c r="Z152" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA152" s="10" t="n">
-        <v>1</v>
+      <c r="AA152" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB152" s="4" t="n"/>
       <c r="AC152" s="4" t="inlineStr"/>
@@ -16243,15 +16243,15 @@
         </is>
       </c>
       <c r="C153" s="4" t="n">
-        <v>9180</v>
+        <v>5040</v>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Thai Airways International Club</t>
+          <t>Siam Toastmasters Club</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" s="6" t="n">
         <v>10</v>
@@ -16265,13 +16265,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J153" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>0</v>
       </c>
       <c r="Q153" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R153" s="9" t="n">
         <v>0</v>
@@ -16310,19 +16310,19 @@
         <v>0</v>
       </c>
       <c r="V153" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X153" s="10" t="n">
-        <v>5</v>
+      <c r="X153" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y153" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z153" s="10" t="n">
-        <v>1</v>
+      <c r="Z153" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA153" s="10" t="n">
         <v>1</v>
@@ -16338,19 +16338,19 @@
       </c>
       <c r="B154" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C154" s="4" t="n">
-        <v>28676629</v>
+        <v>9180</v>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Bilingual Elites Toastmasters Club</t>
+          <t>Thai Airways International Club</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F154" s="6" t="n">
         <v>10</v>
@@ -16364,17 +16364,17 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="J154" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L154" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L154" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M154" s="8" t="n">
@@ -16394,7 +16394,7 @@
         <v>0</v>
       </c>
       <c r="Q154" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R154" s="9" t="n">
         <v>0</v>
@@ -16402,20 +16402,20 @@
       <c r="S154" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T154" s="10" t="n">
-        <v>1</v>
+      <c r="T154" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V154" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W154" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X154" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y154" s="9" t="n">
         <v>0</v>
@@ -16441,15 +16441,15 @@
         </is>
       </c>
       <c r="C155" s="4" t="n">
-        <v>4943786</v>
+        <v>28676629</v>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Empower Toastmasters</t>
+          <t>Bilingual Elites Toastmasters Club</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F155" s="6" t="n">
         <v>10</v>
@@ -16463,13 +16463,13 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="J155" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
@@ -16477,11 +16477,11 @@
         </is>
       </c>
       <c r="M155" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N155" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O155" s="7" t="inlineStr">
@@ -16490,31 +16490,31 @@
         </is>
       </c>
       <c r="P155" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q155" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R155" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T155" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="T155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U155" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V155" s="10" t="n">
-        <v>4</v>
+      <c r="V155" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W155" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X155" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y155" s="9" t="n">
         <v>0</v>
@@ -16522,8 +16522,8 @@
       <c r="Z155" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA155" s="9" t="n">
-        <v>0</v>
+      <c r="AA155" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB155" s="4" t="n"/>
       <c r="AC155" s="4" t="inlineStr"/>
@@ -16540,15 +16540,15 @@
         </is>
       </c>
       <c r="C156" s="4" t="n">
-        <v>7584028</v>
+        <v>4943786</v>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Leaders Toastmasters Club</t>
+          <t>Empower Toastmasters</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16562,25 +16562,25 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="J156" s="4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L156" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M156" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N156" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O156" s="7" t="inlineStr">
@@ -16589,7 +16589,7 @@
         </is>
       </c>
       <c r="P156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q156" s="9" t="n">
         <v>0</v>
@@ -16598,7 +16598,7 @@
         <v>0</v>
       </c>
       <c r="S156" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T156" s="9" t="n">
         <v>0</v>
@@ -16606,23 +16606,23 @@
       <c r="U156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V156" s="9" t="n">
-        <v>1</v>
+      <c r="V156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X156" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="X156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y156" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z156" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA156" s="10" t="n">
-        <v>1</v>
+      <c r="Z156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA156" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB156" s="4" t="n"/>
       <c r="AC156" s="4" t="inlineStr"/>
@@ -16639,11 +16639,11 @@
         </is>
       </c>
       <c r="C157" s="4" t="n">
-        <v>28679537</v>
+        <v>7584028</v>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>RICE Toastmasters Club</t>
+          <t>Leaders Toastmasters Club</t>
         </is>
       </c>
       <c r="E157" s="5" t="n">
@@ -16661,13 +16661,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16675,11 +16675,11 @@
         </is>
       </c>
       <c r="M157" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N157" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O157" s="7" t="inlineStr">
@@ -16706,13 +16706,13 @@
         <v>0</v>
       </c>
       <c r="V157" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W157" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X157" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y157" s="9" t="n">
         <v>0</v>
@@ -16720,8 +16720,8 @@
       <c r="Z157" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA157" s="9" t="n">
-        <v>0</v>
+      <c r="AA157" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB157" s="4" t="n"/>
       <c r="AC157" s="4" t="inlineStr"/>
@@ -16738,11 +16738,11 @@
         </is>
       </c>
       <c r="C158" s="4" t="n">
-        <v>28679273</v>
+        <v>28679537</v>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Slytherin Toastmasters Club</t>
+          <t>RICE Toastmasters Club</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
@@ -16760,10 +16760,10 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J158" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K158" s="4" t="n">
         <v>0</v>
@@ -16837,15 +16837,15 @@
         </is>
       </c>
       <c r="C159" s="4" t="n">
-        <v>28676566</v>
+        <v>28679273</v>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>Sukhumvit Toastmasters Club</t>
+          <t>Slytherin Toastmasters Club</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159" s="6" t="n">
         <v>10</v>
@@ -16859,17 +16859,17 @@
         </is>
       </c>
       <c r="I159" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J159" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K159" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L159" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L159" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M159" s="8" t="n">
@@ -16886,7 +16886,7 @@
         </is>
       </c>
       <c r="P159" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q159" s="9" t="n">
         <v>0</v>
@@ -16903,20 +16903,20 @@
       <c r="U159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V159" s="10" t="n">
-        <v>4</v>
+      <c r="V159" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X159" s="10" t="n">
-        <v>4</v>
+      <c r="X159" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y159" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z159" s="10" t="n">
-        <v>1</v>
+      <c r="Z159" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA159" s="9" t="n">
         <v>0</v>
@@ -16927,24 +16927,24 @@
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C160" s="4" t="n">
-        <v>7848369</v>
+        <v>28676566</v>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>English Teacher Toastmaster</t>
+          <t>Sukhumvit Toastmasters Club</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F160" s="6" t="n">
         <v>10</v>
@@ -16958,10 +16958,10 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J160" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
         <v>4</v>
@@ -16972,11 +16972,11 @@
         </is>
       </c>
       <c r="M160" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N160" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O160" s="7" t="inlineStr">
@@ -16985,19 +16985,19 @@
         </is>
       </c>
       <c r="P160" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q160" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R160" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S160" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T160" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U160" s="9" t="n">
         <v>0</v>
@@ -17017,8 +17017,8 @@
       <c r="Z160" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA160" s="10" t="n">
-        <v>1</v>
+      <c r="AA160" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB160" s="4" t="n"/>
       <c r="AC160" s="4" t="inlineStr"/>
@@ -17035,15 +17035,15 @@
         </is>
       </c>
       <c r="C161" s="4" t="n">
-        <v>1665430</v>
+        <v>7848369</v>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>Hanoi Speakers</t>
+          <t>English Teacher Toastmaster</t>
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F161" s="6" t="n">
         <v>10</v>
@@ -17057,17 +17057,17 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J161" s="4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L161" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M161" s="8" t="n">
@@ -17084,25 +17084,25 @@
         </is>
       </c>
       <c r="P161" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R161" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S161" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V161" s="9" t="n">
-        <v>2</v>
+      <c r="V161" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W161" s="9" t="n">
         <v>0</v>
@@ -17113,8 +17113,8 @@
       <c r="Y161" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z161" s="9" t="n">
-        <v>0</v>
+      <c r="Z161" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA161" s="10" t="n">
         <v>1</v>
@@ -17134,15 +17134,15 @@
         </is>
       </c>
       <c r="C162" s="4" t="n">
-        <v>7581455</v>
+        <v>1665430</v>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>Hanoi Toastmasters</t>
+          <t>Hanoi Speakers</t>
         </is>
       </c>
       <c r="E162" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" s="6" t="n">
         <v>10</v>
@@ -17156,17 +17156,17 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J162" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L162" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L162" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M162" s="8" t="n">
@@ -17183,7 +17183,7 @@
         </is>
       </c>
       <c r="P162" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q162" s="9" t="n">
         <v>0</v>
@@ -17201,19 +17201,19 @@
         <v>0</v>
       </c>
       <c r="V162" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W162" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X162" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y162" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z162" s="10" t="n">
-        <v>1</v>
+      <c r="Z162" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA162" s="10" t="n">
         <v>1</v>
@@ -17233,11 +17233,11 @@
         </is>
       </c>
       <c r="C163" s="4" t="n">
-        <v>28675955</v>
+        <v>7581455</v>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>Hanoi Xplorers Toastmasters</t>
+          <t>Hanoi Toastmasters</t>
         </is>
       </c>
       <c r="E163" s="5" t="n">
@@ -17255,17 +17255,17 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J163" s="4" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L163" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M163" s="8" t="n">
@@ -17282,16 +17282,16 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q163" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R163" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S163" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T163" s="9" t="n">
         <v>0</v>
@@ -17299,20 +17299,20 @@
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="10" t="n">
-        <v>4</v>
+      <c r="V163" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W163" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X163" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z163" s="9" t="n">
-        <v>0</v>
+      <c r="Z163" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA163" s="10" t="n">
         <v>1</v>
@@ -17332,11 +17332,11 @@
         </is>
       </c>
       <c r="C164" s="4" t="n">
-        <v>7953590</v>
+        <v>28675955</v>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>Vietnam Online Toastmasters</t>
+          <t>Hanoi Xplorers Toastmasters</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
@@ -17354,13 +17354,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J164" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17383,8 +17383,8 @@
       <c r="P164" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" s="10" t="n">
-        <v>2</v>
+      <c r="Q164" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="R164" s="9" t="n">
         <v>0</v>
@@ -17398,8 +17398,8 @@
       <c r="U164" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V164" s="9" t="n">
-        <v>3</v>
+      <c r="V164" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W164" s="9" t="n">
         <v>0</v>
@@ -17427,19 +17427,19 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C165" s="4" t="n">
-        <v>5708761</v>
+        <v>7953590</v>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>Danang Toastmasters Club</t>
+          <t>Vietnam Online Toastmasters</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17453,13 +17453,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J165" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -17480,16 +17480,16 @@
         </is>
       </c>
       <c r="P165" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q165" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R165" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T165" s="9" t="n">
         <v>0</v>
@@ -17498,19 +17498,19 @@
         <v>0</v>
       </c>
       <c r="V165" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X165" s="9" t="n">
-        <v>0</v>
+      <c r="X165" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z165" s="9" t="n">
-        <v>0</v>
+      <c r="Z165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA165" s="10" t="n">
         <v>1</v>
@@ -17530,15 +17530,15 @@
         </is>
       </c>
       <c r="C166" s="4" t="n">
-        <v>7881440</v>
+        <v>5708761</v>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>English Vietnamese Online Toastmasters Club</t>
+          <t>Danang Toastmasters Club</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" s="6" t="n">
         <v>10</v>
@@ -17552,17 +17552,17 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J166" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L166" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L166" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M166" s="8" t="n">
@@ -17597,19 +17597,19 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X166" s="10" t="n">
-        <v>5</v>
+      <c r="X166" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y166" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z166" s="10" t="n">
-        <v>1</v>
+      <c r="Z166" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA166" s="10" t="n">
         <v>1</v>
@@ -17629,15 +17629,15 @@
         </is>
       </c>
       <c r="C167" s="4" t="n">
-        <v>28678777</v>
+        <v>7881440</v>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>Heineken VN Toastmasters</t>
+          <t>English Vietnamese Online Toastmasters Club</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17651,25 +17651,25 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J167" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L167" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>2</v>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N167" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O167" s="7" t="inlineStr">
@@ -17696,22 +17696,22 @@
         <v>0</v>
       </c>
       <c r="V167" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X167" s="9" t="n">
-        <v>0</v>
+      <c r="X167" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z167" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA167" s="9" t="n">
-        <v>0</v>
+      <c r="Z167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA167" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB167" s="4" t="n"/>
       <c r="AC167" s="4" t="inlineStr"/>
@@ -17728,11 +17728,11 @@
         </is>
       </c>
       <c r="C168" s="4" t="n">
-        <v>28677991</v>
+        <v>28678777</v>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>Hoian Toastmasters Club</t>
+          <t>Heineken VN Toastmasters</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
@@ -17750,10 +17750,10 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J168" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K168" s="4" t="n">
         <v>0</v>
@@ -17827,11 +17827,11 @@
         </is>
       </c>
       <c r="C169" s="4" t="n">
-        <v>6743137</v>
+        <v>28677991</v>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>Hue Toastmasters Club</t>
+          <t>Hoian Toastmasters Club</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
@@ -17849,10 +17849,10 @@
         </is>
       </c>
       <c r="I169" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J169" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K169" s="4" t="n">
         <v>0</v>
@@ -17863,11 +17863,11 @@
         </is>
       </c>
       <c r="M169" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N169" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O169" s="7" t="inlineStr">
@@ -17899,8 +17899,8 @@
       <c r="W169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X169" s="10" t="n">
-        <v>4</v>
+      <c r="X169" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y169" s="9" t="n">
         <v>0</v>
@@ -17908,8 +17908,8 @@
       <c r="Z169" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA169" s="10" t="n">
-        <v>1</v>
+      <c r="AA169" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB169" s="4" t="n"/>
       <c r="AC169" s="4" t="inlineStr"/>
@@ -17926,11 +17926,11 @@
         </is>
       </c>
       <c r="C170" s="4" t="n">
-        <v>6962498</v>
+        <v>6743137</v>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>Yup Danang Leaders Toastmasters</t>
+          <t>Hue Toastmasters Club</t>
         </is>
       </c>
       <c r="E170" s="5" t="n">
@@ -17948,10 +17948,10 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J170" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K170" s="4" t="n">
         <v>0</v>
@@ -17962,11 +17962,11 @@
         </is>
       </c>
       <c r="M170" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N170" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O170" s="7" t="inlineStr">
@@ -17998,8 +17998,8 @@
       <c r="W170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X170" s="9" t="n">
-        <v>0</v>
+      <c r="X170" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y170" s="9" t="n">
         <v>0</v>
@@ -18007,8 +18007,8 @@
       <c r="Z170" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA170" s="9" t="n">
-        <v>0</v>
+      <c r="AA170" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB170" s="4" t="n"/>
       <c r="AC170" s="4" t="inlineStr"/>
@@ -18021,19 +18021,19 @@
       </c>
       <c r="B171" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C171" s="4" t="n">
-        <v>7892406</v>
+        <v>6962498</v>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>ACI Toastmasters Online</t>
+          <t>Yup Danang Leaders Toastmasters</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F171" s="6" t="n">
         <v>10</v>
@@ -18047,25 +18047,25 @@
         </is>
       </c>
       <c r="I171" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J171" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K171" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L171" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L171" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M171" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N171" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O171" s="7" t="inlineStr">
@@ -18074,7 +18074,7 @@
         </is>
       </c>
       <c r="P171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q171" s="9" t="n">
         <v>0</v>
@@ -18092,22 +18092,22 @@
         <v>0</v>
       </c>
       <c r="V171" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X171" s="10" t="n">
-        <v>4</v>
+      <c r="X171" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y171" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z171" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA171" s="10" t="n">
-        <v>1</v>
+      <c r="Z171" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA171" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB171" s="4" t="n"/>
       <c r="AC171" s="4" t="inlineStr"/>
@@ -18124,15 +18124,15 @@
         </is>
       </c>
       <c r="C172" s="4" t="n">
-        <v>28677872</v>
+        <v>7892406</v>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>C-Level Advanced Toastmasters Club</t>
+          <t>ACI Toastmasters Online</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F172" s="6" t="n">
         <v>10</v>
@@ -18146,17 +18146,17 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="J172" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L172" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M172" s="8" t="n">
@@ -18173,7 +18173,7 @@
         </is>
       </c>
       <c r="P172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
         <v>0</v>
@@ -18184,14 +18184,14 @@
       <c r="S172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T172" s="9" t="n">
-        <v>0</v>
+      <c r="T172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U172" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W172" s="9" t="n">
         <v>0</v>
@@ -18202,8 +18202,8 @@
       <c r="Y172" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z172" s="9" t="n">
-        <v>0</v>
+      <c r="Z172" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA172" s="10" t="n">
         <v>1</v>
@@ -18223,15 +18223,15 @@
         </is>
       </c>
       <c r="C173" s="4" t="n">
-        <v>28675656</v>
+        <v>28677872</v>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>ESO Toastmasters</t>
+          <t>C-Level Advanced Toastmasters Club</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F173" s="6" t="n">
         <v>10</v>
@@ -18245,13 +18245,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J173" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -18272,10 +18272,10 @@
         </is>
       </c>
       <c r="P173" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q173" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R173" s="9" t="n">
         <v>0</v>
@@ -18283,14 +18283,14 @@
       <c r="S173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T173" s="10" t="n">
-        <v>1</v>
+      <c r="T173" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U173" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V173" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W173" s="9" t="n">
         <v>0</v>
@@ -18301,8 +18301,8 @@
       <c r="Y173" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z173" s="10" t="n">
-        <v>1</v>
+      <c r="Z173" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA173" s="10" t="n">
         <v>1</v>
@@ -18322,15 +18322,15 @@
         </is>
       </c>
       <c r="C174" s="4" t="n">
-        <v>28677773</v>
+        <v>28675656</v>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>FLA Toastmasters</t>
+          <t>ESO Toastmasters</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18344,13 +18344,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J174" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="P174" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q174" s="9" t="n">
         <v>1</v>
@@ -18382,14 +18382,14 @@
       <c r="S174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T174" s="9" t="n">
-        <v>0</v>
+      <c r="T174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U174" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V174" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
@@ -18400,8 +18400,8 @@
       <c r="Y174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z174" s="9" t="n">
-        <v>0</v>
+      <c r="Z174" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA174" s="10" t="n">
         <v>1</v>
@@ -18421,15 +18421,15 @@
         </is>
       </c>
       <c r="C175" s="4" t="n">
-        <v>28676675</v>
+        <v>28677773</v>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>VITA Toastmasters</t>
+          <t>FLA Toastmasters</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F175" s="6" t="n">
         <v>10</v>
@@ -18443,13 +18443,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J175" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18470,10 +18470,10 @@
         </is>
       </c>
       <c r="P175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q175" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R175" s="9" t="n">
         <v>0</v>
@@ -18481,26 +18481,26 @@
       <c r="S175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T175" s="10" t="n">
-        <v>1</v>
+      <c r="T175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U175" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V175" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W175" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X175" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y175" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z175" s="10" t="n">
-        <v>1</v>
+      <c r="Z175" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA175" s="10" t="n">
         <v>1</v>
@@ -18516,19 +18516,19 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C176" s="4" t="n">
-        <v>4409462</v>
+        <v>28676675</v>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>HCM Toastmasters Club</t>
+          <t>VITA Toastmasters</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F176" s="6" t="n">
         <v>10</v>
@@ -18542,17 +18542,17 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J176" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L176" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L176" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M176" s="8" t="n">
@@ -18569,31 +18569,31 @@
         </is>
       </c>
       <c r="P176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T176" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U176" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V176" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S176" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T176" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U176" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V176" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="W176" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X176" s="9" t="n">
-        <v>2</v>
+      <c r="X176" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y176" s="9" t="n">
         <v>0</v>
@@ -18619,15 +18619,15 @@
         </is>
       </c>
       <c r="C177" s="4" t="n">
-        <v>28679145</v>
+        <v>4409462</v>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>Saigon Dynamics Toastmasters Club</t>
+          <t>HCM Toastmasters Club</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F177" s="6" t="n">
         <v>10</v>
@@ -18641,13 +18641,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="J177" s="4" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -18668,7 +18668,7 @@
         </is>
       </c>
       <c r="P177" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q177" s="9" t="n">
         <v>0</v>
@@ -18679,20 +18679,20 @@
       <c r="S177" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T177" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U177" s="9" t="n">
-        <v>0</v>
+      <c r="T177" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U177" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V177" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W177" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="X177" s="10" t="n">
-        <v>5</v>
+      <c r="W177" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X177" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y177" s="9" t="n">
         <v>0</v>
@@ -18718,15 +18718,15 @@
         </is>
       </c>
       <c r="C178" s="4" t="n">
-        <v>1513681</v>
+        <v>28679145</v>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>Saigon Toastmasters Club</t>
+          <t>Saigon Dynamics Toastmasters Club</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F178" s="6" t="n">
         <v>10</v>
@@ -18740,13 +18740,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="J178" s="4" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -18767,7 +18767,7 @@
         </is>
       </c>
       <c r="P178" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q178" s="9" t="n">
         <v>0</v>
@@ -18776,7 +18776,7 @@
         <v>0</v>
       </c>
       <c r="S178" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T178" s="9" t="n">
         <v>0</v>
@@ -18784,11 +18784,11 @@
       <c r="U178" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V178" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W178" s="9" t="n">
-        <v>0</v>
+      <c r="V178" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W178" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X178" s="10" t="n">
         <v>5</v>
@@ -18817,15 +18817,15 @@
         </is>
       </c>
       <c r="C179" s="4" t="n">
-        <v>2786174</v>
+        <v>1513681</v>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>UEH-ISB Toastmasters</t>
+          <t>Saigon Toastmasters Club</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18839,25 +18839,25 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="J179" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="K179" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="J179" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="K179" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M179" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N179" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O179" s="7" t="inlineStr">
@@ -18875,7 +18875,7 @@
         <v>0</v>
       </c>
       <c r="S179" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T179" s="9" t="n">
         <v>0</v>
@@ -18883,23 +18883,23 @@
       <c r="U179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X179" s="9" t="n">
-        <v>0</v>
+      <c r="V179" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W179" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="X179" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y179" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z179" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA179" s="9" t="n">
-        <v>0</v>
+      <c r="Z179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB179" s="4" t="n"/>
       <c r="AC179" s="4" t="inlineStr"/>
@@ -18916,15 +18916,15 @@
         </is>
       </c>
       <c r="C180" s="4" t="n">
-        <v>5614099</v>
+        <v>2786174</v>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Vietnam Leaders Toastmasters</t>
+          <t>UEH-ISB Toastmasters</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -18938,25 +18938,25 @@
         </is>
       </c>
       <c r="I180" s="4" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="J180" s="4" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="K180" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L180" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L180" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M180" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N180" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O180" s="7" t="inlineStr">
@@ -18982,14 +18982,14 @@
       <c r="U180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V180" s="10" t="n">
-        <v>4</v>
+      <c r="V180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W180" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X180" s="10" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="X180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y180" s="9" t="n">
         <v>0</v>
@@ -18997,8 +18997,8 @@
       <c r="Z180" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA180" s="10" t="n">
-        <v>1</v>
+      <c r="AA180" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB180" s="4" t="n"/>
       <c r="AC180" s="4" t="inlineStr"/>
@@ -19006,24 +19006,24 @@
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>V</t>
         </is>
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>04</t>
         </is>
       </c>
       <c r="C181" s="4" t="n">
-        <v>2357700</v>
+        <v>5614099</v>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>BP Bangsar South Toastmasters Club</t>
+          <t>Vietnam Leaders Toastmasters</t>
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19037,13 +19037,13 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J181" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
@@ -19064,31 +19064,31 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U181" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V181" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W181" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q181" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S181" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T181" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V181" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W181" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="X181" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y181" s="9" t="n">
         <v>0</v>
@@ -19099,14 +19099,8 @@
       <c r="AA181" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB181" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC181" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+      <c r="AB181" s="4" t="n"/>
+      <c r="AC181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -19120,15 +19114,15 @@
         </is>
       </c>
       <c r="C182" s="4" t="n">
-        <v>7903951</v>
+        <v>2357700</v>
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>ESG-MIA High Achiever Grooming Toastmasters Club</t>
+          <t>BP Bangsar South Toastmasters Club</t>
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19142,17 +19136,17 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J182" s="4" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L182" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L182" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M182" s="8" t="n">
@@ -19171,23 +19165,23 @@
       <c r="P182" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q182" s="10" t="n">
+      <c r="Q182" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R182" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S182" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R182" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S182" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T182" s="9" t="n">
-        <v>0</v>
+      <c r="T182" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V182" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W182" s="9" t="n">
         <v>0</v>
@@ -19205,9 +19199,13 @@
         <v>1</v>
       </c>
       <c r="AB182" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC182" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC182" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -19221,15 +19219,15 @@
         </is>
       </c>
       <c r="C183" s="4" t="n">
-        <v>28678619</v>
+        <v>7903951</v>
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Marriott Malaysia Toastmasters Club</t>
+          <t>ESG-MIA High Achiever Grooming Toastmasters Club</t>
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F183" s="6" t="n">
         <v>10</v>
@@ -19243,17 +19241,17 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J183" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L183" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L183" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M183" s="8" t="n">
@@ -19270,16 +19268,16 @@
         </is>
       </c>
       <c r="P183" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q183" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q183" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T183" s="9" t="n">
         <v>0</v>
@@ -19288,25 +19286,25 @@
         <v>0</v>
       </c>
       <c r="V183" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W183" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X183" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y183" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB183" s="4" t="n">
         <v>7</v>
-      </c>
-      <c r="Y183" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z183" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA183" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB183" s="4" t="n">
-        <v>9</v>
       </c>
       <c r="AC183" s="4" t="inlineStr"/>
     </row>
@@ -19322,15 +19320,15 @@
         </is>
       </c>
       <c r="C184" s="4" t="n">
-        <v>8052</v>
+        <v>28678619</v>
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Telekom Malaysia Toastmasters Club, KL</t>
+          <t>Marriott Malaysia Toastmasters Club</t>
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19344,17 +19342,17 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="J184" s="4" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K184" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L184" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M184" s="8" t="n">
@@ -19395,19 +19393,19 @@
         <v>0</v>
       </c>
       <c r="X184" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z184" s="9" t="n">
-        <v>0</v>
+      <c r="Z184" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA184" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB184" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AC184" s="4" t="inlineStr"/>
     </row>
@@ -19423,15 +19421,15 @@
         </is>
       </c>
       <c r="C185" s="4" t="n">
-        <v>28679542</v>
+        <v>8052</v>
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>TNB Genco Toastmasters Club</t>
+          <t>Telekom Malaysia Toastmasters Club, KL</t>
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F185" s="6" t="n">
         <v>10</v>
@@ -19445,17 +19443,17 @@
         </is>
       </c>
       <c r="I185" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J185" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K185" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L185" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L185" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M185" s="8" t="n">
@@ -19495,20 +19493,20 @@
       <c r="W185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X185" s="9" t="n">
-        <v>0</v>
+      <c r="X185" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y185" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z185" s="9" t="n">
-        <v>0</v>
+      <c r="Z185" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA185" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB185" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC185" s="4" t="inlineStr"/>
     </row>
@@ -19524,15 +19522,15 @@
         </is>
       </c>
       <c r="C186" s="4" t="n">
-        <v>1028031</v>
+        <v>28679542</v>
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>University Malaya Toastmasters Club</t>
+          <t>TNB Genco Toastmasters Club</t>
         </is>
       </c>
       <c r="E186" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186" s="6" t="n">
         <v>10</v>
@@ -19546,10 +19544,10 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J186" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K186" s="4" t="n">
         <v>0</v>
@@ -19596,26 +19594,22 @@
       <c r="W186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X186" s="10" t="n">
-        <v>7</v>
+      <c r="X186" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y186" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z186" s="10" t="n">
-        <v>1</v>
+      <c r="Z186" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA186" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB186" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC186" s="4" t="inlineStr">
-        <is>
-          <t>Smedley Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -19625,19 +19619,19 @@
       </c>
       <c r="B187" s="4" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="C187" s="4" t="n">
-        <v>2106318</v>
+        <v>1028031</v>
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>BASF KL Toastmasters Club</t>
+          <t>University Malaya Toastmasters Club</t>
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19651,17 +19645,17 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="J187" s="4" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="K187" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L187" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L187" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M187" s="8" t="n">
@@ -19678,16 +19672,16 @@
         </is>
       </c>
       <c r="P187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R187" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S187" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T187" s="9" t="n">
         <v>0</v>
@@ -19702,21 +19696,25 @@
         <v>0</v>
       </c>
       <c r="X187" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z187" s="9" t="n">
-        <v>0</v>
+      <c r="Z187" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA187" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB187" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC187" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC187" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -19730,15 +19728,15 @@
         </is>
       </c>
       <c r="C188" s="4" t="n">
-        <v>28676437</v>
+        <v>2106318</v>
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>BHP KL Toastmasters Club</t>
+          <t>BASF KL Toastmasters Club</t>
         </is>
       </c>
       <c r="E188" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F188" s="6" t="n">
         <v>10</v>
@@ -19752,10 +19750,10 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J188" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K188" s="4" t="n">
         <v>0</v>
@@ -19779,7 +19777,7 @@
         </is>
       </c>
       <c r="P188" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q188" s="9" t="n">
         <v>1</v>
@@ -19788,10 +19786,10 @@
         <v>0</v>
       </c>
       <c r="S188" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T188" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T188" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U188" s="9" t="n">
         <v>0</v>
@@ -19815,7 +19813,7 @@
         <v>1</v>
       </c>
       <c r="AB188" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC188" s="4" t="inlineStr"/>
     </row>
@@ -19831,15 +19829,15 @@
         </is>
       </c>
       <c r="C189" s="4" t="n">
-        <v>3567460</v>
+        <v>28676437</v>
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Kijang Toastmasters Club</t>
+          <t>BHP KL Toastmasters Club</t>
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -19853,10 +19851,10 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J189" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K189" s="4" t="n">
         <v>0</v>
@@ -19883,13 +19881,13 @@
         <v>0</v>
       </c>
       <c r="Q189" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S189" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T189" s="9" t="n">
         <v>0</v>
@@ -19909,20 +19907,16 @@
       <c r="Y189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z189" s="9" t="n">
-        <v>0</v>
+      <c r="Z189" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA189" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB189" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC189" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -19936,11 +19930,11 @@
         </is>
       </c>
       <c r="C190" s="4" t="n">
-        <v>6895</v>
+        <v>3567460</v>
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>MAICSA Toastmasters Club</t>
+          <t>Kijang Toastmasters Club</t>
         </is>
       </c>
       <c r="E190" s="5" t="n">
@@ -19958,17 +19952,17 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J190" s="4" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L190" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L190" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M190" s="8" t="n">
@@ -19994,7 +19988,7 @@
         <v>0</v>
       </c>
       <c r="S190" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T190" s="9" t="n">
         <v>0</v>
@@ -20003,7 +19997,7 @@
         <v>0</v>
       </c>
       <c r="V190" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W190" s="9" t="n">
         <v>0</v>
@@ -20021,11 +20015,11 @@
         <v>1</v>
       </c>
       <c r="AB190" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC190" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -20041,15 +20035,15 @@
         </is>
       </c>
       <c r="C191" s="4" t="n">
-        <v>5364172</v>
+        <v>6895</v>
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>UNIRAZAK Toastmasters Club</t>
+          <t>MAICSA Toastmasters Club</t>
         </is>
       </c>
       <c r="E191" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" s="6" t="n">
         <v>10</v>
@@ -20063,25 +20057,25 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J191" s="4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L191" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M191" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N191" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O191" s="7" t="inlineStr">
@@ -20090,7 +20084,7 @@
         </is>
       </c>
       <c r="P191" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q191" s="9" t="n">
         <v>0</v>
@@ -20099,7 +20093,7 @@
         <v>0</v>
       </c>
       <c r="S191" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T191" s="9" t="n">
         <v>0</v>
@@ -20108,13 +20102,13 @@
         <v>0</v>
       </c>
       <c r="V191" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W191" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X191" s="9" t="n">
-        <v>0</v>
+      <c r="X191" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y191" s="9" t="n">
         <v>0</v>
@@ -20122,13 +20116,17 @@
       <c r="Z191" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA191" s="9" t="n">
-        <v>0</v>
+      <c r="AA191" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AB191" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC191" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC191" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -20138,15 +20136,15 @@
       </c>
       <c r="B192" s="4" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="C192" s="4" t="n">
-        <v>28676862</v>
+        <v>5364172</v>
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>FGV Toastmasters Club</t>
+          <t>UNIRAZAK Toastmasters Club</t>
         </is>
       </c>
       <c r="E192" s="5" t="n">
@@ -20164,10 +20162,10 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="J192" s="4" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="K192" s="4" t="n">
         <v>0</v>
@@ -20191,7 +20189,7 @@
         </is>
       </c>
       <c r="P192" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q192" s="9" t="n">
         <v>0</v>
@@ -20200,7 +20198,7 @@
         <v>0</v>
       </c>
       <c r="S192" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T192" s="9" t="n">
         <v>0</v>
@@ -20220,14 +20218,14 @@
       <c r="Y192" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z192" s="9" t="n">
-        <v>0</v>
+      <c r="Z192" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA192" s="9" t="n">
         <v>0</v>
       </c>
       <c r="AB192" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC192" s="4" t="inlineStr"/>
     </row>
@@ -20243,11 +20241,11 @@
         </is>
       </c>
       <c r="C193" s="4" t="n">
-        <v>7494595</v>
+        <v>28676862</v>
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Pro Speakers and Trainers Toastmasters Club</t>
+          <t>FGV Toastmasters Club</t>
         </is>
       </c>
       <c r="E193" s="5" t="n">
@@ -20265,10 +20263,10 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J193" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K193" s="4" t="n">
         <v>0</v>
@@ -20279,11 +20277,11 @@
         </is>
       </c>
       <c r="M193" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N193" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O193" s="7" t="inlineStr">
@@ -20324,11 +20322,11 @@
       <c r="Z193" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA193" s="10" t="n">
-        <v>1</v>
+      <c r="AA193" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AB193" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC193" s="4" t="inlineStr"/>
     </row>
@@ -20344,11 +20342,11 @@
         </is>
       </c>
       <c r="C194" s="4" t="n">
-        <v>28678087</v>
+        <v>7494595</v>
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Securities Commission Toastmasters Club</t>
+          <t>Pro Speakers and Trainers Toastmasters Club</t>
         </is>
       </c>
       <c r="E194" s="5" t="n">
@@ -20366,17 +20364,17 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="J194" s="4" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K194" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L194" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L194" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M194" s="8" t="n">
@@ -20393,7 +20391,7 @@
         </is>
       </c>
       <c r="P194" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q194" s="9" t="n">
         <v>0</v>
@@ -20416,8 +20414,8 @@
       <c r="W194" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X194" s="10" t="n">
-        <v>7</v>
+      <c r="X194" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y194" s="9" t="n">
         <v>0</v>
@@ -20429,13 +20427,9 @@
         <v>1</v>
       </c>
       <c r="AB194" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC194" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -20449,11 +20443,11 @@
         </is>
       </c>
       <c r="C195" s="4" t="n">
-        <v>220</v>
+        <v>28678087</v>
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Speakers' Dream Toastmasters</t>
+          <t>Securities Commission Toastmasters Club</t>
         </is>
       </c>
       <c r="E195" s="5" t="n">
@@ -20471,10 +20465,10 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J195" s="4" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K195" s="4" t="n">
         <v>0</v>
@@ -20498,7 +20492,7 @@
         </is>
       </c>
       <c r="P195" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q195" s="9" t="n">
         <v>0</v>
@@ -20521,8 +20515,8 @@
       <c r="W195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X195" s="9" t="n">
-        <v>0</v>
+      <c r="X195" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y195" s="9" t="n">
         <v>0</v>
@@ -20534,11 +20528,11 @@
         <v>1</v>
       </c>
       <c r="AB195" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AC195" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -20554,15 +20548,15 @@
         </is>
       </c>
       <c r="C196" s="4" t="n">
-        <v>5111</v>
+        <v>220</v>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>TTDI Toastmasters Club</t>
+          <t>Speakers' Dream Toastmasters</t>
         </is>
       </c>
       <c r="E196" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F196" s="6" t="n">
         <v>10</v>
@@ -20576,13 +20570,13 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="J196" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
@@ -20603,7 +20597,7 @@
         </is>
       </c>
       <c r="P196" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q196" s="9" t="n">
         <v>0</v>
@@ -20614,26 +20608,26 @@
       <c r="S196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T196" s="10" t="n">
-        <v>1</v>
+      <c r="T196" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U196" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V196" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X196" s="10" t="n">
-        <v>4</v>
+      <c r="X196" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y196" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z196" s="10" t="n">
-        <v>1</v>
+      <c r="Z196" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA196" s="10" t="n">
         <v>1</v>
@@ -20655,15 +20649,15 @@
       </c>
       <c r="B197" s="4" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="C197" s="4" t="n">
-        <v>3793732</v>
+        <v>5111</v>
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>Elite Toastmasters Club</t>
+          <t>TTDI Toastmasters Club</t>
         </is>
       </c>
       <c r="E197" s="5" t="n">
@@ -20681,10 +20675,10 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J197" s="4" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K197" s="4" t="n">
         <v>2</v>
@@ -20708,10 +20702,10 @@
         </is>
       </c>
       <c r="P197" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q197" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R197" s="9" t="n">
         <v>0</v>
@@ -20732,7 +20726,7 @@
         <v>0</v>
       </c>
       <c r="X197" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y197" s="9" t="n">
         <v>0</v>
@@ -20744,11 +20738,11 @@
         <v>1</v>
       </c>
       <c r="AB197" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC197" s="4" t="inlineStr">
         <is>
-          <t>Smedley Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -20764,15 +20758,15 @@
         </is>
       </c>
       <c r="C198" s="4" t="n">
-        <v>950005</v>
+        <v>3793732</v>
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>Great Eastern Toastmasters Club</t>
+          <t>Elite Toastmasters Club</t>
         </is>
       </c>
       <c r="E198" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F198" s="6" t="n">
         <v>10</v>
@@ -20786,13 +20780,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="J198" s="4" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
@@ -20813,7 +20807,7 @@
         </is>
       </c>
       <c r="P198" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q198" s="9" t="n">
         <v>1</v>
@@ -20822,7 +20816,7 @@
         <v>0</v>
       </c>
       <c r="S198" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T198" s="10" t="n">
         <v>1</v>
@@ -20831,19 +20825,19 @@
         <v>0</v>
       </c>
       <c r="V198" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W198" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X198" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y198" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z198" s="9" t="n">
-        <v>0</v>
+      <c r="Z198" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA198" s="10" t="n">
         <v>1</v>
@@ -20869,15 +20863,15 @@
         </is>
       </c>
       <c r="C199" s="4" t="n">
-        <v>2426124</v>
+        <v>950005</v>
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>OCBC Toastmasters Club</t>
+          <t>Great Eastern Toastmasters Club</t>
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -20891,17 +20885,17 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J199" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="K199" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L199" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L199" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M199" s="8" t="n">
@@ -20918,19 +20912,19 @@
         </is>
       </c>
       <c r="P199" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q199" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R199" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S199" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T199" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T199" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U199" s="9" t="n">
         <v>0</v>
@@ -20942,7 +20936,7 @@
         <v>0</v>
       </c>
       <c r="X199" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y199" s="9" t="n">
         <v>0</v>
@@ -20954,9 +20948,13 @@
         <v>1</v>
       </c>
       <c r="AB199" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC199" s="4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="AC199" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -20970,15 +20968,15 @@
         </is>
       </c>
       <c r="C200" s="4" t="n">
-        <v>1589773</v>
+        <v>2426124</v>
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>Oneworld Toastmasters Club</t>
+          <t>OCBC Toastmasters Club</t>
         </is>
       </c>
       <c r="E200" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F200" s="6" t="n">
         <v>10</v>
@@ -20992,17 +20990,17 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J200" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K200" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L200" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L200" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M200" s="8" t="n">
@@ -21022,7 +21020,7 @@
         <v>0</v>
       </c>
       <c r="Q200" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R200" s="9" t="n">
         <v>0</v>
@@ -21030,8 +21028,8 @@
       <c r="S200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T200" s="10" t="n">
-        <v>1</v>
+      <c r="T200" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U200" s="9" t="n">
         <v>0</v>
@@ -21043,25 +21041,21 @@
         <v>0</v>
       </c>
       <c r="X200" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y200" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z200" s="10" t="n">
-        <v>1</v>
+      <c r="Z200" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA200" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB200" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC200" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -21075,15 +21069,15 @@
         </is>
       </c>
       <c r="C201" s="4" t="n">
-        <v>6883550</v>
+        <v>1589773</v>
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>RHB Toastmasters Club</t>
+          <t>Oneworld Toastmasters Club</t>
         </is>
       </c>
       <c r="E201" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" s="6" t="n">
         <v>10</v>
@@ -21127,16 +21121,16 @@
         <v>0</v>
       </c>
       <c r="Q201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R201" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S201" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T201" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U201" s="9" t="n">
         <v>0</v>
@@ -21148,7 +21142,7 @@
         <v>0</v>
       </c>
       <c r="X201" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y201" s="9" t="n">
         <v>0</v>
@@ -21160,7 +21154,7 @@
         <v>1</v>
       </c>
       <c r="AB201" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC201" s="4" t="inlineStr">
         <is>
@@ -21180,15 +21174,15 @@
         </is>
       </c>
       <c r="C202" s="4" t="n">
-        <v>1759651</v>
+        <v>6883550</v>
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>TARUMT KL Toastmasters Club</t>
+          <t>RHB Toastmasters Club</t>
         </is>
       </c>
       <c r="E202" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F202" s="6" t="n">
         <v>10</v>
@@ -21202,13 +21196,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J202" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
@@ -21229,48 +21223,153 @@
         </is>
       </c>
       <c r="P202" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q202" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X202" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y202" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB202" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC202" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="n">
+        <v>1759651</v>
+      </c>
+      <c r="D203" s="4" t="inlineStr">
+        <is>
+          <t>TARUMT KL Toastmasters Club</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G203" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H203" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J203" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K203" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="L203" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M203" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O203" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P203" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R202" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V202" s="10" t="n">
+      <c r="Q203" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R203" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V203" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W202" s="9" t="n">
+      <c r="W203" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="X202" s="10" t="n">
+      <c r="X203" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Y202" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z202" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA202" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB202" s="4" t="n">
+      <c r="Y203" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB203" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="AC202" s="4" t="inlineStr"/>
+      <c r="AC203" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC202"/>
+  <autoFilter ref="A1:AC203"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21357,7 +21456,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -21390,7 +21489,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21423,7 +21522,7 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -21456,7 +21555,7 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -21489,7 +21588,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21654,7 +21753,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -21687,7 +21786,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -21720,7 +21819,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -21852,7 +21951,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21885,7 +21984,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21918,7 +22017,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -21951,7 +22050,7 @@
         <v>6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -21984,7 +22083,7 @@
         <v>4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -22083,7 +22182,7 @@
         <v>5</v>
       </c>
       <c r="D24" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -22149,7 +22248,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22212,16 +22311,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -22230,7 +22329,7 @@
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -22248,7 +22347,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.43</v>
+        <v>0.57</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22380,7 +22479,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22446,7 +22545,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22479,7 +22578,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -22512,7 +22611,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -22545,7 +22644,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 55 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 53 clubs short</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -906,8 +906,8 @@
       <c r="U2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="9" t="n">
-        <v>3</v>
+      <c r="V2" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1060,17 +1060,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>2</v>
+      </c>
+      <c r="L4" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="8" t="n">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1258,17 +1258,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L6" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M6" s="8" t="n">
@@ -1302,11 +1302,11 @@
       <c r="U6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V6" s="9" t="n">
-        <v>3</v>
+      <c r="V6" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W6" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6" s="10" t="n">
         <v>6</v>
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L7" s="7" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1500,8 +1500,8 @@
       <c r="U8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V8" s="9" t="n">
-        <v>2</v>
+      <c r="V8" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1555,13 +1555,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W10" s="9" t="n">
         <v>0</v>
@@ -1753,17 +1753,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L11" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="8" t="n">
@@ -1798,7 +1798,7 @@
         <v>3</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1852,13 +1852,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
@@ -1884,14 +1884,14 @@
       <c r="Q12" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R12" s="9" t="n">
-        <v>1</v>
+      <c r="R12" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S12" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="T12" s="9" t="n">
-        <v>0</v>
+      <c r="T12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U12" s="9" t="n">
         <v>0</v>
@@ -2050,17 +2050,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L14" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="8" t="n">
@@ -2149,13 +2149,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2347,17 +2347,17 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-24</v>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M17" s="8" t="n">
@@ -2545,17 +2545,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="8" t="n">
@@ -2646,17 +2646,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="8" t="n">
@@ -2852,13 +2852,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>2</v>
       </c>
       <c r="V22" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W22" s="9" t="n">
         <v>0</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3058,13 +3058,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
@@ -3163,17 +3163,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3268,13 +3268,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
@@ -3369,13 +3369,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3514,11 +3514,11 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>3</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X28" s="10" t="n">
         <v>7</v>
@@ -3575,17 +3575,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-22</v>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="8" t="n">
@@ -3676,17 +3676,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3878,17 +3878,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L32" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="8" t="n">
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="6" t="n">
         <v>10</v>
@@ -3983,13 +3983,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -4030,8 +4030,8 @@
       <c r="V33" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W33" s="9" t="n">
-        <v>2</v>
+      <c r="W33" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X33" s="10" t="n">
         <v>6</v>
@@ -4389,13 +4389,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W37" s="9" t="n">
         <v>0</v>
@@ -4480,7 +4480,7 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="6" t="n">
         <v>10</v>
@@ -4532,14 +4532,14 @@
       <c r="S38" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="9" t="n">
-        <v>0</v>
+      <c r="T38" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U38" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V38" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W38" s="9" t="n">
         <v>0</v>
@@ -4599,17 +4599,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -4704,17 +4704,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="8" t="n">
@@ -4910,13 +4910,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="6" t="n">
         <v>10</v>
@@ -5011,13 +5011,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5055,11 +5055,11 @@
       <c r="U43" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V43" s="9" t="n">
-        <v>1</v>
+      <c r="V43" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>6</v>
@@ -5116,13 +5116,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W44" s="9" t="n">
         <v>0</v>
@@ -5326,13 +5326,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>4</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5431,17 +5431,17 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L47" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M47" s="8" t="n">
@@ -5536,17 +5536,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5581,7 +5581,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5742,13 +5742,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="6" t="n">
         <v>10</v>
@@ -5843,17 +5843,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -5872,8 +5872,8 @@
       <c r="P51" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" s="9" t="n">
-        <v>1</v>
+      <c r="Q51" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R51" s="9" t="n">
         <v>0</v>
@@ -5888,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5948,17 +5948,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L52" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="8" t="n">
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
@@ -5996,7 +5996,7 @@
         <v>4</v>
       </c>
       <c r="W52" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X52" s="10" t="n">
         <v>7</v>
@@ -6035,7 +6035,7 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6049,13 +6049,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -6093,11 +6093,11 @@
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V53" s="9" t="n">
-        <v>1</v>
+      <c r="V53" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W53" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X53" s="10" t="n">
         <v>5</v>
@@ -6150,17 +6150,17 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L54" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M54" s="8" t="n">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6255,13 +6255,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6299,8 +6299,8 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>2</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6356,17 +6356,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6506,7 +6506,7 @@
         <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="6" t="n">
         <v>10</v>
@@ -6663,17 +6663,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L59" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="8" t="n">
@@ -6701,8 +6701,8 @@
       <c r="S59" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T59" s="9" t="n">
-        <v>0</v>
+      <c r="T59" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U59" s="9" t="n">
         <v>0</v>
@@ -6768,13 +6768,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6869,17 +6869,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-29</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6974,17 +6974,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L62" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="8" t="n">
@@ -7019,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7079,13 +7079,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7178,13 +7178,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -7324,7 +7324,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7384,13 +7384,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7485,13 +7485,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7572,7 +7572,7 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7586,17 +7586,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="8" t="n">
@@ -7624,14 +7624,14 @@
       <c r="S68" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T68" s="9" t="n">
-        <v>0</v>
+      <c r="T68" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U68" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7691,13 +7691,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>47</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
@@ -7717,14 +7717,14 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P69" s="9" t="n">
-        <v>3</v>
+      <c r="P69" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q69" s="10" t="n">
         <v>2</v>
       </c>
       <c r="R69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" s="9" t="n">
         <v>0</v>
@@ -7739,7 +7739,7 @@
         <v>4</v>
       </c>
       <c r="W69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X69" s="10" t="n">
         <v>7</v>
@@ -7895,13 +7895,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
@@ -7996,13 +7996,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -8101,13 +8101,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -8202,13 +8202,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -8247,7 +8247,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -8303,13 +8303,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8404,13 +8404,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8509,13 +8509,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8550,11 +8550,11 @@
       <c r="T77" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
+      <c r="U77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
@@ -8715,13 +8715,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -8820,17 +8820,17 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L80" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M80" s="8" t="n">
@@ -8850,7 +8850,7 @@
         <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8865,7 +8865,7 @@
         <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
@@ -8907,7 +8907,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8921,17 +8921,17 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L81" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M81" s="8" t="n">
@@ -8965,11 +8965,11 @@
       <c r="U81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V81" s="9" t="n">
-        <v>1</v>
+      <c r="V81" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W81" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X81" s="10" t="n">
         <v>7</v>
@@ -8977,8 +8977,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -9074,7 +9074,7 @@
         <v>4</v>
       </c>
       <c r="W82" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X82" s="10" t="n">
         <v>4</v>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -9228,13 +9228,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
@@ -9272,11 +9272,11 @@
       <c r="U84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V84" s="9" t="n">
-        <v>1</v>
+      <c r="V84" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W84" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X84" s="10" t="n">
         <v>6</v>
@@ -9333,17 +9333,17 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L85" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M85" s="8" t="n">
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9438,17 +9438,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9486,7 +9486,7 @@
         <v>4</v>
       </c>
       <c r="W86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X86" s="10" t="n">
         <v>5</v>
@@ -9543,13 +9543,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>36</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-13</v>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
@@ -9588,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
@@ -9648,17 +9648,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9753,13 +9753,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>0</v>
       </c>
       <c r="V89" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W89" s="9" t="n">
         <v>0</v>
@@ -9858,13 +9858,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>52</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
@@ -9963,13 +9963,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -10068,17 +10068,17 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L92" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L92" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M92" s="8" t="n">
@@ -10173,13 +10173,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -10274,13 +10274,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -10375,17 +10375,17 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L95" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M95" s="8" t="n">
@@ -10476,13 +10476,13 @@
         </is>
       </c>
       <c r="I96" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J96" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K96" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L97" s="7" t="inlineStr">
         <is>
@@ -10678,13 +10678,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10779,13 +10779,13 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10880,17 +10880,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10985,13 +10985,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -11086,17 +11086,17 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L102" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M102" s="8" t="n">
@@ -11191,13 +11191,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         </is>
       </c>
       <c r="P103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q103" s="9" t="n">
         <v>0</v>
@@ -11292,17 +11292,17 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L104" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L104" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M104" s="8" t="n">
@@ -11397,13 +11397,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11589,7 +11589,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11603,13 +11603,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L107" s="7" t="inlineStr">
         <is>
@@ -11647,11 +11647,11 @@
       <c r="U107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V107" s="9" t="n">
-        <v>3</v>
+      <c r="V107" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W107" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X107" s="10" t="n">
         <v>4</v>
@@ -11704,13 +11704,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11805,17 +11805,17 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L109" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M109" s="8" t="n">
@@ -11910,13 +11910,13 @@
         </is>
       </c>
       <c r="I110" s="4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J110" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K110" s="4" t="n">
-        <v>3</v>
+        <v>-9</v>
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
@@ -12015,17 +12015,17 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L111" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L111" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M111" s="8" t="n">
@@ -12120,17 +12120,17 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L112" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L112" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M112" s="8" t="n">
@@ -12225,13 +12225,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -12532,17 +12532,17 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L116" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L116" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M116" s="8" t="n">
@@ -12637,13 +12637,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12738,13 +12738,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12940,17 +12940,17 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L120" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L120" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M120" s="8" t="n">
@@ -13031,7 +13031,7 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -13045,13 +13045,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
@@ -13089,11 +13089,11 @@
       <c r="U121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V121" s="9" t="n">
-        <v>3</v>
+      <c r="V121" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W121" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X121" s="10" t="n">
         <v>7</v>
@@ -13150,13 +13150,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         </is>
       </c>
       <c r="P122" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>1</v>
@@ -13186,7 +13186,7 @@
         <v>0</v>
       </c>
       <c r="S122" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T122" s="10" t="n">
         <v>1</v>
@@ -13241,7 +13241,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -13299,8 +13299,8 @@
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V123" s="9" t="n">
-        <v>0</v>
+      <c r="V123" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
@@ -13356,17 +13356,17 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L124" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L124" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M124" s="8" t="n">
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13461,13 +13461,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13505,11 +13505,11 @@
       <c r="U125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V125" s="9" t="n">
-        <v>0</v>
+      <c r="V125" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W125" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>7</v>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13663,13 +13663,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J127" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
@@ -13865,13 +13865,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>4</v>
       </c>
       <c r="W129" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X129" s="9" t="n">
         <v>0</v>
@@ -13966,13 +13966,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" s="6" t="n">
         <v>10</v>
@@ -14123,8 +14123,8 @@
       <c r="Y131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z131" s="9" t="n">
-        <v>0</v>
+      <c r="Z131" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA131" s="10" t="n">
         <v>1</v>
@@ -14166,13 +14166,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
@@ -14271,13 +14271,13 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -14316,7 +14316,7 @@
         <v>1</v>
       </c>
       <c r="V133" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W133" s="9" t="n">
         <v>0</v>
@@ -14463,7 +14463,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -14477,13 +14477,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
@@ -14524,8 +14524,8 @@
       <c r="V135" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W135" s="9" t="n">
-        <v>3</v>
+      <c r="W135" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X135" s="10" t="n">
         <v>7</v>
@@ -14568,7 +14568,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -14620,8 +14620,8 @@
       <c r="S136" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T136" s="9" t="n">
-        <v>0</v>
+      <c r="T136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U136" s="9" t="n">
         <v>0</v>
@@ -14681,13 +14681,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -14780,13 +14780,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14978,13 +14978,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -15077,13 +15077,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -15176,13 +15176,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -15206,7 +15206,7 @@
         <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15275,13 +15275,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -15319,11 +15319,11 @@
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W143" s="9" t="n">
-        <v>0</v>
+      <c r="V143" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W143" s="10" t="n">
+        <v>9</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>4</v>
@@ -15459,7 +15459,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -15473,13 +15473,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -15517,8 +15517,8 @@
       <c r="U145" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V145" s="9" t="n">
-        <v>3</v>
+      <c r="V145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
@@ -15572,13 +15572,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>5</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -15770,13 +15770,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15869,13 +15869,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15968,13 +15968,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>5</v>
+        <v>-16</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X150" s="10" t="n">
         <v>4</v>
@@ -16067,13 +16067,13 @@
         </is>
       </c>
       <c r="I151" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J151" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K151" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L151" s="7" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>1</v>
       </c>
       <c r="V151" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W151" s="9" t="n">
         <v>0</v>
@@ -16265,13 +16265,13 @@
         </is>
       </c>
       <c r="I153" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J153" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K153" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L153" s="7" t="inlineStr">
         <is>
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="I154" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J154" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K154" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L154" s="7" t="inlineStr">
         <is>
@@ -16463,17 +16463,17 @@
         </is>
       </c>
       <c r="I155" s="4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="J155" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K155" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L155" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L155" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M155" s="8" t="n">
@@ -16562,13 +16562,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>4</v>
       </c>
       <c r="W156" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X156" s="10" t="n">
         <v>4</v>
@@ -16661,13 +16661,13 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J157" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K157" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L157" s="7" t="inlineStr">
         <is>
@@ -16760,13 +16760,13 @@
         </is>
       </c>
       <c r="I158" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J158" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K158" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L158" s="7" t="inlineStr">
         <is>
@@ -16958,17 +16958,17 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L160" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L160" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M160" s="8" t="n">
@@ -17006,7 +17006,7 @@
         <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>4</v>
@@ -17057,13 +17057,13 @@
         </is>
       </c>
       <c r="I161" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J161" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K161" s="4" t="n">
-        <v>4</v>
+        <v>-5</v>
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
@@ -17105,7 +17105,7 @@
         <v>4</v>
       </c>
       <c r="W161" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X161" s="10" t="n">
         <v>4</v>
@@ -17156,13 +17156,13 @@
         </is>
       </c>
       <c r="I162" s="4" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="J162" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K162" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L162" s="7" t="inlineStr">
         <is>
@@ -17241,7 +17241,7 @@
         </is>
       </c>
       <c r="E163" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F163" s="6" t="n">
         <v>10</v>
@@ -17255,13 +17255,13 @@
         </is>
       </c>
       <c r="I163" s="4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J163" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K163" s="4" t="n">
-        <v>3</v>
+        <v>-5</v>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
@@ -17299,11 +17299,11 @@
       <c r="U163" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V163" s="9" t="n">
-        <v>3</v>
+      <c r="V163" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W163" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X163" s="10" t="n">
         <v>5</v>
@@ -17354,13 +17354,13 @@
         </is>
       </c>
       <c r="I164" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J164" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K164" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L164" s="7" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17497,8 +17497,8 @@
       <c r="U165" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V165" s="9" t="n">
-        <v>3</v>
+      <c r="V165" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W165" s="9" t="n">
         <v>0</v>
@@ -17552,13 +17552,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>0</v>
       </c>
       <c r="V166" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W166" s="9" t="n">
         <v>0</v>
@@ -17637,7 +17637,7 @@
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" s="6" t="n">
         <v>10</v>
@@ -17651,17 +17651,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L167" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L167" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -17695,11 +17695,11 @@
       <c r="U167" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V167" s="9" t="n">
-        <v>2</v>
+      <c r="V167" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W167" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X167" s="10" t="n">
         <v>5</v>
@@ -17750,13 +17750,13 @@
         </is>
       </c>
       <c r="I168" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J168" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K168" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L168" s="7" t="inlineStr">
         <is>
@@ -17948,13 +17948,13 @@
         </is>
       </c>
       <c r="I170" s="4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J170" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K170" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L170" s="7" t="inlineStr">
         <is>
@@ -18146,17 +18146,17 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L172" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L172" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M172" s="8" t="n">
@@ -18245,13 +18245,13 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J173" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K173" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L173" s="7" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F174" s="6" t="n">
         <v>10</v>
@@ -18344,13 +18344,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -18388,8 +18388,8 @@
       <c r="U174" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V174" s="9" t="n">
-        <v>2</v>
+      <c r="V174" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W174" s="9" t="n">
         <v>0</v>
@@ -18443,13 +18443,13 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J175" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K175" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L175" s="7" t="inlineStr">
         <is>
@@ -18542,13 +18542,13 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J176" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K176" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L176" s="7" t="inlineStr">
         <is>
@@ -18641,13 +18641,13 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J177" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K177" s="4" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
@@ -18689,7 +18689,7 @@
         <v>4</v>
       </c>
       <c r="W177" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X177" s="9" t="n">
         <v>2</v>
@@ -18740,13 +18740,13 @@
         </is>
       </c>
       <c r="I178" s="4" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="J178" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K178" s="4" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>4</v>
       </c>
       <c r="W178" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="X178" s="10" t="n">
         <v>5</v>
@@ -18825,7 +18825,7 @@
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F179" s="6" t="n">
         <v>10</v>
@@ -18839,13 +18839,13 @@
         </is>
       </c>
       <c r="I179" s="4" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J179" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K179" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
@@ -18877,8 +18877,8 @@
       <c r="S179" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T179" s="9" t="n">
-        <v>0</v>
+      <c r="T179" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U179" s="9" t="n">
         <v>0</v>
@@ -18924,7 +18924,7 @@
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" s="6" t="n">
         <v>10</v>
@@ -18982,8 +18982,8 @@
       <c r="U180" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V180" s="9" t="n">
-        <v>0</v>
+      <c r="V180" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W180" s="9" t="n">
         <v>0</v>
@@ -19023,7 +19023,7 @@
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F181" s="6" t="n">
         <v>10</v>
@@ -19037,17 +19037,17 @@
         </is>
       </c>
       <c r="I181" s="4" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J181" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K181" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L181" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L181" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M181" s="8" t="n">
@@ -19064,7 +19064,7 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q181" s="9" t="n">
         <v>0</v>
@@ -19084,8 +19084,8 @@
       <c r="V181" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W181" s="9" t="n">
-        <v>2</v>
+      <c r="W181" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X181" s="10" t="n">
         <v>5</v>
@@ -19122,7 +19122,7 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F182" s="6" t="n">
         <v>10</v>
@@ -19136,13 +19136,13 @@
         </is>
       </c>
       <c r="I182" s="4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J182" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K182" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
@@ -19163,7 +19163,7 @@
         </is>
       </c>
       <c r="P182" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q182" s="9" t="n">
         <v>1</v>
@@ -19180,11 +19180,11 @@
       <c r="U182" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V182" s="9" t="n">
-        <v>0</v>
+      <c r="V182" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W182" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X182" s="10" t="n">
         <v>4</v>
@@ -19241,13 +19241,13 @@
         </is>
       </c>
       <c r="I183" s="4" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J183" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K183" s="4" t="n">
-        <v>1</v>
+        <v>-6</v>
       </c>
       <c r="L183" s="7" t="inlineStr">
         <is>
@@ -19328,7 +19328,7 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F184" s="6" t="n">
         <v>10</v>
@@ -19342,13 +19342,13 @@
         </is>
       </c>
       <c r="I184" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J184" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K184" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
@@ -19386,11 +19386,11 @@
       <c r="U184" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V184" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W184" s="9" t="n">
-        <v>0</v>
+      <c r="V184" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W184" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X184" s="10" t="n">
         <v>7</v>
@@ -19544,17 +19544,17 @@
         </is>
       </c>
       <c r="I186" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J186" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K186" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L186" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M186" s="8" t="n">
@@ -19631,7 +19631,7 @@
         </is>
       </c>
       <c r="E187" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F187" s="6" t="n">
         <v>10</v>
@@ -19645,13 +19645,13 @@
         </is>
       </c>
       <c r="I187" s="4" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J187" s="4" t="n">
         <v>30</v>
       </c>
       <c r="K187" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
@@ -19689,8 +19689,8 @@
       <c r="U187" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V187" s="9" t="n">
-        <v>0</v>
+      <c r="V187" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W187" s="9" t="n">
         <v>0</v>
@@ -19750,13 +19750,13 @@
         </is>
       </c>
       <c r="I188" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J188" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K188" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L188" s="7" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         <v>0</v>
       </c>
       <c r="V188" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W188" s="9" t="n">
         <v>0</v>
@@ -19837,7 +19837,7 @@
         </is>
       </c>
       <c r="E189" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F189" s="6" t="n">
         <v>10</v>
@@ -19851,13 +19851,13 @@
         </is>
       </c>
       <c r="I189" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J189" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K189" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L189" s="7" t="inlineStr">
         <is>
@@ -19880,8 +19880,8 @@
       <c r="P189" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" s="9" t="n">
-        <v>1</v>
+      <c r="Q189" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R189" s="9" t="n">
         <v>0</v>
@@ -19952,13 +19952,13 @@
         </is>
       </c>
       <c r="I190" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J190" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K190" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L190" s="7" t="inlineStr">
         <is>
@@ -20057,13 +20057,13 @@
         </is>
       </c>
       <c r="I191" s="4" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J191" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K191" s="4" t="n">
-        <v>3</v>
+        <v>-6</v>
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
@@ -20162,13 +20162,13 @@
         </is>
       </c>
       <c r="I192" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J192" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K192" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L192" s="7" t="inlineStr">
         <is>
@@ -20263,13 +20263,13 @@
         </is>
       </c>
       <c r="I193" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J193" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K193" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L193" s="7" t="inlineStr">
         <is>
@@ -20364,13 +20364,13 @@
         </is>
       </c>
       <c r="I194" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J194" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K194" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L194" s="7" t="inlineStr">
         <is>
@@ -20465,17 +20465,17 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L195" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-33</v>
+      </c>
+      <c r="L195" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M195" s="8" t="n">
@@ -20570,17 +20570,17 @@
         </is>
       </c>
       <c r="I196" s="4" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J196" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K196" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-20</v>
+      </c>
+      <c r="L196" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M196" s="8" t="n">
@@ -20675,13 +20675,13 @@
         </is>
       </c>
       <c r="I197" s="4" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J197" s="4" t="n">
         <v>31</v>
       </c>
       <c r="K197" s="4" t="n">
-        <v>2</v>
+        <v>-6</v>
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
@@ -20702,10 +20702,10 @@
         </is>
       </c>
       <c r="P197" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q197" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R197" s="9" t="n">
         <v>0</v>
@@ -20780,13 +20780,13 @@
         </is>
       </c>
       <c r="I198" s="4" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J198" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K198" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
@@ -20885,17 +20885,17 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L199" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-25</v>
+      </c>
+      <c r="L199" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M199" s="8" t="n">
@@ -20990,13 +20990,13 @@
         </is>
       </c>
       <c r="I200" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J200" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K200" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L200" s="7" t="inlineStr">
         <is>
@@ -21091,17 +21091,17 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L201" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L201" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M201" s="8" t="n">
@@ -21136,7 +21136,7 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -21196,17 +21196,17 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L202" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-11</v>
+      </c>
+      <c r="L202" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M202" s="8" t="n">
@@ -21287,7 +21287,7 @@
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F203" s="6" t="n">
         <v>10</v>
@@ -21301,17 +21301,17 @@
         </is>
       </c>
       <c r="I203" s="4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J203" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K203" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L203" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L203" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M203" s="8" t="n">
@@ -21328,13 +21328,13 @@
         </is>
       </c>
       <c r="P203" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q203" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="R203" s="9" t="n">
-        <v>1</v>
+      <c r="R203" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="S203" s="9" t="n">
         <v>0</v>
@@ -21456,7 +21456,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -21471,7 +21471,7 @@
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -21489,7 +21489,7 @@
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -21522,13 +21522,13 @@
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -21537,7 +21537,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -21570,7 +21570,7 @@
         <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -21603,7 +21603,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -21621,7 +21621,7 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -21636,7 +21636,7 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -21654,7 +21654,7 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -21669,7 +21669,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -21687,7 +21687,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -21702,7 +21702,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -21720,7 +21720,7 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -21735,7 +21735,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -21768,7 +21768,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -21786,7 +21786,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -21801,7 +21801,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -21819,7 +21819,7 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -21834,7 +21834,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -21867,7 +21867,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -21885,13 +21885,13 @@
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -21900,7 +21900,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -21951,7 +21951,7 @@
         <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -21984,7 +21984,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -21999,7 +21999,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -22032,7 +22032,7 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -22065,7 +22065,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -22098,7 +22098,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -22131,7 +22131,7 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -22149,7 +22149,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -22164,7 +22164,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -22197,7 +22197,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -22215,13 +22215,13 @@
         <v>4</v>
       </c>
       <c r="D25" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -22230,7 +22230,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -22248,7 +22248,7 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -22263,7 +22263,7 @@
         <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -22314,7 +22314,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -22347,7 +22347,7 @@
         <v>7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22461,7 +22461,7 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -22479,7 +22479,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22512,7 +22512,7 @@
         <v>6</v>
       </c>
       <c r="D34" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -22545,7 +22545,7 @@
         <v>5</v>
       </c>
       <c r="D35" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -22560,7 +22560,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -22578,7 +22578,7 @@
         <v>5</v>
       </c>
       <c r="D36" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -22593,7 +22593,7 @@
         <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -22611,7 +22611,7 @@
         <v>6</v>
       </c>
       <c r="D37" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -22626,7 +22626,7 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -22644,7 +22644,7 @@
         <v>5</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -22710,7 +22710,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -22725,7 +22725,7 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 53 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 52 clubs short</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="P14" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" s="10" t="n">
         <v>2</v>
@@ -2943,7 +2943,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -2957,13 +2957,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3001,11 +3001,11 @@
       <c r="U23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V23" s="9" t="n">
-        <v>0</v>
+      <c r="V23" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W23" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X23" s="10" t="n">
         <v>7</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="P44" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q44" s="10" t="n">
         <v>2</v>
@@ -5563,10 +5563,10 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6855,7 +6855,7 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F61" s="6" t="n">
         <v>10</v>
@@ -6869,17 +6869,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-29</v>
-      </c>
-      <c r="L61" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6913,8 +6913,8 @@
       <c r="U61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V61" s="9" t="n">
-        <v>0</v>
+      <c r="V61" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6925,8 +6925,8 @@
       <c r="Y61" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z61" s="9" t="n">
-        <v>0</v>
+      <c r="Z61" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA61" s="10" t="n">
         <v>1</v>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7009,8 +7009,8 @@
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="9" t="n">
-        <v>1</v>
+      <c r="S62" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T62" s="9" t="n">
         <v>0</v>
@@ -7079,13 +7079,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="P69" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q69" s="10" t="n">
         <v>2</v>
@@ -8137,7 +8137,7 @@
         <v>0</v>
       </c>
       <c r="S73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T73" s="9" t="n">
         <v>0</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>0</v>
@@ -9258,13 +9258,13 @@
         <v>0</v>
       </c>
       <c r="Q84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" s="10" t="n">
         <v>1</v>
@@ -9333,13 +9333,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         <v>0</v>
       </c>
       <c r="V85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W85" s="9" t="n">
         <v>0</v>
@@ -9438,13 +9438,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L86" s="7" t="inlineStr">
         <is>
@@ -9990,7 +9990,7 @@
         </is>
       </c>
       <c r="P91" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
         <v>0</v>
@@ -11424,7 +11424,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -13136,7 +13136,7 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F122" s="6" t="n">
         <v>10</v>
@@ -13150,13 +13150,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
@@ -13176,8 +13176,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P122" s="9" t="n">
-        <v>3</v>
+      <c r="P122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q122" s="9" t="n">
         <v>1</v>
@@ -13194,8 +13194,8 @@
       <c r="U122" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V122" s="9" t="n">
-        <v>3</v>
+      <c r="V122" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W122" s="9" t="n">
         <v>0</v>
@@ -13447,7 +13447,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -13461,13 +13461,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J125" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
@@ -13508,8 +13508,8 @@
       <c r="V125" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W125" s="9" t="n">
-        <v>2</v>
+      <c r="W125" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X125" s="10" t="n">
         <v>7</v>
@@ -13562,13 +13562,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-16</v>
+        <v>-7</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13750,7 +13750,7 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13802,11 +13802,11 @@
       <c r="S128" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="T128" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" s="9" t="n">
-        <v>0</v>
+      <c r="T128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V128" s="9" t="n">
         <v>2</v>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -14204,8 +14204,8 @@
       <c r="S132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T132" s="9" t="n">
-        <v>0</v>
+      <c r="T132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U132" s="9" t="n">
         <v>0</v>
@@ -15261,7 +15261,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -15275,13 +15275,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -15302,7 +15302,7 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q143" s="9" t="n">
         <v>1</v>
@@ -15311,10 +15311,10 @@
         <v>0</v>
       </c>
       <c r="S143" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T143" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U143" s="9" t="n">
         <v>0</v>
@@ -15323,7 +15323,7 @@
         <v>4</v>
       </c>
       <c r="W143" s="10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>4</v>
@@ -16548,7 +16548,7 @@
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F156" s="6" t="n">
         <v>10</v>
@@ -16562,13 +16562,13 @@
         </is>
       </c>
       <c r="I156" s="4" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J156" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K156" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
@@ -16609,8 +16609,8 @@
       <c r="V156" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W156" s="9" t="n">
-        <v>3</v>
+      <c r="W156" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X156" s="10" t="n">
         <v>4</v>
@@ -16958,13 +16958,13 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J160" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K160" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L160" s="7" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>4</v>
       </c>
       <c r="W160" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X160" s="10" t="n">
         <v>4</v>
@@ -17453,13 +17453,13 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J165" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K165" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L165" s="7" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>4</v>
       </c>
       <c r="W165" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X165" s="10" t="n">
         <v>4</v>
@@ -17552,13 +17552,13 @@
         </is>
       </c>
       <c r="I166" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J166" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K166" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L166" s="7" t="inlineStr">
         <is>
@@ -18176,7 +18176,7 @@
         <v>1</v>
       </c>
       <c r="Q172" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R172" s="9" t="n">
         <v>0</v>
@@ -18371,7 +18371,7 @@
         </is>
       </c>
       <c r="P174" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q174" s="9" t="n">
         <v>1</v>
@@ -19672,7 +19672,7 @@
         </is>
       </c>
       <c r="P187" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q187" s="9" t="n">
         <v>0</v>
@@ -20087,7 +20087,7 @@
         <v>0</v>
       </c>
       <c r="Q191" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R191" s="9" t="n">
         <v>0</v>
@@ -20451,7 +20451,7 @@
         </is>
       </c>
       <c r="E195" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" s="6" t="n">
         <v>10</v>
@@ -20465,17 +20465,17 @@
         </is>
       </c>
       <c r="I195" s="4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="J195" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K195" s="4" t="n">
-        <v>-33</v>
-      </c>
-      <c r="L195" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-1</v>
+      </c>
+      <c r="L195" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M195" s="8" t="n">
@@ -20509,11 +20509,11 @@
       <c r="U195" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V195" s="9" t="n">
-        <v>0</v>
+      <c r="V195" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W195" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X195" s="10" t="n">
         <v>7</v>
@@ -21588,7 +21588,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -21852,7 +21852,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -21867,7 +21867,7 @@
         <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -22248,13 +22248,13 @@
         <v>4</v>
       </c>
       <c r="D26" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -22281,7 +22281,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -22314,7 +22314,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -22380,7 +22380,7 @@
         <v>7</v>
       </c>
       <c r="D30" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -22446,7 +22446,7 @@
         <v>6</v>
       </c>
       <c r="D32" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -22677,7 +22677,7 @@
         <v>5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">

--- a/docs/d/51/inyear.xlsx
+++ b/docs/d/51/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 27 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 27 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 52 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 52 clubs short</t>
         </is>
       </c>
     </row>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1063,10 +1063,10 @@
         <v>5</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="S14" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T14" s="10" t="n">
         <v>1</v>
@@ -2646,13 +2646,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q28" s="9" t="n">
         <v>1</v>
@@ -4599,17 +4599,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L39" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W39" s="9" t="n">
         <v>0</v>
@@ -5011,13 +5011,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>4</v>
       </c>
       <c r="W43" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X43" s="10" t="n">
         <v>6</v>
@@ -5417,7 +5417,7 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5469,8 +5469,8 @@
       <c r="S47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T47" s="9" t="n">
-        <v>0</v>
+      <c r="T47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U47" s="9" t="n">
         <v>0</v>
@@ -6768,13 +6768,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -7718,7 +7718,7 @@
         </is>
       </c>
       <c r="P69" s="10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q69" s="10" t="n">
         <v>2</v>
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8101,17 +8101,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K73" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J73" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L73" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="8" t="n">
@@ -8145,11 +8145,11 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W73" s="9" t="n">
-        <v>0</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W73" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>6</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8341,11 +8341,11 @@
       <c r="S75" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V75" s="9" t="n">
         <v>3</v>
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8404,13 +8404,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8451,8 +8451,8 @@
       <c r="V76" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W76" s="9" t="n">
-        <v>3</v>
+      <c r="W76" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X76" s="10" t="n">
         <v>6</v>
@@ -8715,13 +8715,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>1</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" s="6" t="n">
         <v>10</v>
@@ -9362,8 +9362,8 @@
       <c r="P85" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" s="9" t="n">
-        <v>1</v>
+      <c r="Q85" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R85" s="9" t="n">
         <v>0</v>
@@ -9468,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="Q86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R86" s="9" t="n">
         <v>0</v>
@@ -11498,13 +11498,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -12225,13 +12225,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -12664,7 +12664,7 @@
         </is>
       </c>
       <c r="P117" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q117" s="9" t="n">
         <v>0</v>
@@ -13966,13 +13966,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -15770,13 +15770,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15968,13 +15968,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -17282,7 +17282,7 @@
         </is>
       </c>
       <c r="P163" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q163" s="9" t="n">
         <v>0</v>
@@ -17439,7 +17439,7 @@
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F165" s="6" t="n">
         <v>10</v>
@@ -17491,8 +17491,8 @@
       <c r="S165" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T165" s="9" t="n">
-        <v>0</v>
+      <c r="T165" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U165" s="9" t="n">
         <v>0</v>
@@ -17651,17 +17651,17 @@
         </is>
       </c>
       <c r="I167" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J167" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K167" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L167" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M167" s="8" t="n">
@@ -17678,7 +17678,7 @@
         </is>
       </c>
       <c r="P167" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q167" s="9" t="n">
         <v>0</v>
@@ -18146,13 +18146,13 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J172" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K172" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L172" s="7" t="inlineStr">
         <is>
@@ -18344,13 +18344,13 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J174" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K174" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L174" s="7" t="inlineStr">
         <is>
@@ -19064,7 +19064,7 @@
         </is>
       </c>
       <c r="P181" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q181" s="9" t="n">
         <v>0</v>
@@ -20871,7 +20871,7 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F199" s="6" t="n">
         <v>10</v>
@@ -20885,13 +20885,13 @@
         </is>
       </c>
       <c r="I199" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J199" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K199" s="4" t="n">
-        <v>-25</v>
+        <v>-10</v>
       </c>
       <c r="L199" s="7" t="inlineStr">
         <is>
@@ -20929,8 +20929,8 @@
       <c r="U199" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V199" s="9" t="n">
-        <v>0</v>
+      <c r="V199" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W199" s="9" t="n">
         <v>0</v>
@@ -21091,13 +21091,13 @@
         </is>
       </c>
       <c r="I201" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J201" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K201" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L201" s="7" t="inlineStr">
         <is>
@@ -21136,7 +21136,7 @@
         <v>0</v>
       </c>
       <c r="V201" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W201" s="9" t="n">
         <v>0</v>
@@ -21196,13 +21196,13 @@
         </is>
       </c>
       <c r="I202" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J202" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K202" s="4" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="L202" s="7" t="inlineStr">
         <is>
@@ -21702,7 +21702,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -21753,7 +21753,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -21918,7 +21918,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -21933,7 +21933,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -21984,7 +21984,7 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -22479,7 +22479,7 @@
         <v>5</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -22527,7 +22527,7 @@
         <v>3</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -22710,7 +22710,7 @@
         <v>6</v>
       </c>
       <c r="D40" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
